--- a/results/_EC_summary.xlsx
+++ b/results/_EC_summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\naudl\Documents\GitHub\Energy-community-potential-model\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EA7FB1C-D8EE-42D5-ABDA-886581B38EEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F88440DC-F00D-4792-96A7-49FC4DD70327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{2AD6F2B3-B3D8-4900-A927-DF019433309F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2AD6F2B3-B3D8-4900-A927-DF019433309F}"/>
   </bookViews>
   <sheets>
     <sheet name="calibration_statistics" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>year</t>
   </si>
@@ -63,6 +63,12 @@
   </si>
   <si>
     <t>Installed cap (MW)</t>
+  </si>
+  <si>
+    <t>households</t>
+  </si>
+  <si>
+    <t>Members (% of households)</t>
   </si>
 </sst>
 </file>
@@ -435,7 +441,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2F94C2C-27D9-49D2-80F1-03A3F1312A67}">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="9.33203125" bestFit="1" customWidth="1"/>
@@ -443,7 +449,7 @@
     <col min="4" max="9" width="9.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -471,8 +477,14 @@
       <c r="I1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2009</v>
       </c>
@@ -500,8 +512,15 @@
       <c r="I2" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="K2">
+        <v>7.3</v>
+      </c>
+      <c r="L2">
+        <f>C2/K2/1000000*100</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2010</v>
       </c>
@@ -529,8 +548,15 @@
       <c r="I3" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="K3">
+        <v>7.4</v>
+      </c>
+      <c r="L3">
+        <f t="shared" ref="L3:L17" si="0">C3/K3/1000000*100</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2011</v>
       </c>
@@ -558,8 +584,15 @@
       <c r="I4" s="1">
         <v>53.241</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="K4">
+        <v>7.4</v>
+      </c>
+      <c r="L4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2012</v>
       </c>
@@ -587,8 +620,15 @@
       <c r="I5" s="1">
         <v>58.591000000000001</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="K5">
+        <v>7.5</v>
+      </c>
+      <c r="L5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2013</v>
       </c>
@@ -616,8 +656,15 @@
       <c r="I6" s="1">
         <v>71.741</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="K6">
+        <v>7.6</v>
+      </c>
+      <c r="L6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2014</v>
       </c>
@@ -645,8 +692,15 @@
       <c r="I7" s="1">
         <v>72.590999999999994</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="K7">
+        <v>7.6</v>
+      </c>
+      <c r="L7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2015</v>
       </c>
@@ -674,8 +728,15 @@
       <c r="I8" s="1">
         <v>78.515999999999991</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="K8">
+        <v>7.7</v>
+      </c>
+      <c r="L8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2016</v>
       </c>
@@ -703,8 +764,15 @@
       <c r="I9" s="1">
         <v>117.06599999999999</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="K9">
+        <v>7.7</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="0"/>
+        <v>0.66233766233766234</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2017</v>
       </c>
@@ -732,8 +800,15 @@
       <c r="I10" s="1">
         <v>120.98699999999999</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="K10">
+        <v>7.8</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="0"/>
+        <v>0.80769230769230771</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2018</v>
       </c>
@@ -761,8 +836,15 @@
       <c r="I11" s="1">
         <v>166.77699999999999</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="K11">
+        <v>7.9</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="0"/>
+        <v>0.860759493670886</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2019</v>
       </c>
@@ -790,8 +872,15 @@
       <c r="I12" s="1">
         <v>189.89699999999999</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="K12">
+        <v>7.9</v>
+      </c>
+      <c r="L12">
+        <f t="shared" si="0"/>
+        <v>1.1108860759493671</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2020</v>
       </c>
@@ -819,8 +908,15 @@
       <c r="I13" s="1">
         <v>227.017</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="K13">
+        <v>8</v>
+      </c>
+      <c r="L13">
+        <f t="shared" si="0"/>
+        <v>1.2041375000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2021</v>
       </c>
@@ -848,8 +944,15 @@
       <c r="I14" s="1">
         <v>315.38099999999997</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="K14">
+        <v>8</v>
+      </c>
+      <c r="L14">
+        <f t="shared" si="0"/>
+        <v>1.3934500000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2022</v>
       </c>
@@ -877,8 +980,15 @@
       <c r="I15" s="1">
         <v>334.99799999999999</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="K15">
+        <v>8.1</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="0"/>
+        <v>1.4841234567901236</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2023</v>
       </c>
@@ -906,8 +1016,15 @@
       <c r="I16" s="1">
         <v>356.91800000000001</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="K16">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="L16">
+        <f t="shared" si="0"/>
+        <v>1.5804819277108431</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2024</v>
       </c>
@@ -934,6 +1051,13 @@
       </c>
       <c r="I17" s="1">
         <v>365.46800000000002</v>
+      </c>
+      <c r="K17">
+        <v>8.4</v>
+      </c>
+      <c r="L17">
+        <f t="shared" si="0"/>
+        <v>1.6504761904761904</v>
       </c>
     </row>
   </sheetData>

--- a/results/_EC_summary.xlsx
+++ b/results/_EC_summary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\naudl\Documents\GitHub\Energy-community-potential-model\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F88440DC-F00D-4792-96A7-49FC4DD70327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB23AC4B-C9A2-43E9-8A01-B4F16370F344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2AD6F2B3-B3D8-4900-A927-DF019433309F}"/>
+    <workbookView xWindow="1884" yWindow="1884" windowWidth="17280" windowHeight="8880" xr2:uid="{2AD6F2B3-B3D8-4900-A927-DF019433309F}"/>
   </bookViews>
   <sheets>
     <sheet name="calibration_statistics" sheetId="2" r:id="rId1"/>
@@ -1056,7 +1056,7 @@
         <v>8.4</v>
       </c>
       <c r="L17">
-        <f t="shared" si="0"/>
+        <f>C17/K17/1000000*100</f>
         <v>1.6504761904761904</v>
       </c>
     </row>
